--- a/Tuan3/BTTester.xlsx
+++ b/Tuan3/BTTester.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\HCMUNRE\Tester\Tuan3\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{FEE7C6B4-698B-44CC-98CF-18A525C45878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="13" xr2:uid="{121B782D-B8A7-4516-82E1-837A39FCAABF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="14" xr2:uid="{121B782D-B8A7-4516-82E1-837A39FCAABF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tuan2_Lab3_Bai1" sheetId="1" r:id="rId1"/>
@@ -1492,7 +1492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1557,12 +1557,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1574,7 +1568,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1583,8 +1577,38 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1592,38 +1616,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1631,13 +1628,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1649,23 +1646,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1676,21 +1666,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2267,7 +2242,7 @@
       <c r="F1" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="37" t="s">
         <v>192</v>
       </c>
       <c r="H1" s="30" t="s">
@@ -2305,22 +2280,22 @@
       <c r="F2" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="J2" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="K2" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L2" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M2" s="41">
+      <c r="J2" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="K2" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L2" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M2" s="39">
         <v>0</v>
       </c>
     </row>
@@ -2340,22 +2315,22 @@
       <c r="F3" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="J3" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="K3" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L3" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M3" s="41">
+      <c r="J3" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="K3" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L3" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M3" s="39">
         <v>0.05</v>
       </c>
     </row>
@@ -2375,22 +2350,22 @@
       <c r="F4" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="J4" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="K4" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="L4" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M4" s="41">
+      <c r="J4" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="L4" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M4" s="39">
         <v>0.1</v>
       </c>
     </row>
@@ -2410,22 +2385,22 @@
       <c r="F5" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="J5" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="K5" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L5" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="M5" s="41">
+      <c r="J5" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L5" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="M5" s="39">
         <v>0.25</v>
       </c>
     </row>
@@ -2445,22 +2420,22 @@
       <c r="F6" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="J6" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="K6" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="L6" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M6" s="41">
+      <c r="J6" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="K6" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="L6" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M6" s="39">
         <v>0.1</v>
       </c>
     </row>
@@ -2480,22 +2455,22 @@
       <c r="F7" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="H7" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="I7" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="J7" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="K7" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L7" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="M7" s="41">
+      <c r="J7" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="K7" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L7" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="M7" s="39">
         <v>0.25</v>
       </c>
     </row>
@@ -2515,22 +2490,22 @@
       <c r="F8" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="H8" s="40" t="s">
+      <c r="H8" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="38" t="s">
         <v>234</v>
       </c>
-      <c r="J8" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="K8" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="L8" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="M8" s="41">
+      <c r="J8" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="K8" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="L8" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="M8" s="39">
         <v>0.25</v>
       </c>
     </row>
@@ -2550,22 +2525,22 @@
       <c r="F9" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="H9" s="40" t="s">
+      <c r="H9" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" s="38" t="s">
         <v>235</v>
       </c>
-      <c r="J9" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="K9" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="L9" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="M9" s="41">
+      <c r="J9" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="K9" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="L9" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="M9" s="39">
         <v>0.25</v>
       </c>
     </row>
@@ -2575,13 +2550,13 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="32" t="s">
         <v>153</v>
       </c>
       <c r="D12" s="30" t="s">
@@ -2599,7 +2574,7 @@
       <c r="H12" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="I12" s="42" t="s">
+      <c r="I12" s="32" t="s">
         <v>250</v>
       </c>
       <c r="J12" s="30" t="s">
@@ -2619,175 +2594,175 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
-      <c r="B13" s="33" t="s">
+      <c r="A13" s="52"/>
+      <c r="B13" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G13" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H13" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="J13" s="40" t="s">
+      <c r="E13" s="38"/>
+      <c r="F13" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="J13" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="N13" s="41">
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="N13" s="39">
         <v>0.25</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="46"/>
-      <c r="B14" s="33" t="s">
+      <c r="A14" s="53"/>
+      <c r="B14" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="G14" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H14" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="J14" s="40" t="s">
+      <c r="E14" s="38"/>
+      <c r="F14" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="J14" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="K14" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L14" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N14" s="41">
+      <c r="K14" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L14" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="M14" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="N14" s="39">
         <v>0.1</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D15" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="E15" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="F15" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G15" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H15" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="J15" s="40" t="s">
+      <c r="E15" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="J15" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="K15" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="L15" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M15" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N15" s="41">
+      <c r="K15" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="L15" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M15" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="N15" s="39">
         <v>0.05</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
-      <c r="B16" s="33" t="s">
+      <c r="A16" s="52"/>
+      <c r="B16" s="31" t="s">
         <v>243</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="E16" s="40" t="s">
+      <c r="E16" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="J16" s="40" t="s">
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="J16" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="K16" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L16" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M16" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N16" s="41">
+      <c r="K16" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L16" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M16" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="N16" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="44"/>
-      <c r="B17" s="33" t="s">
+      <c r="A17" s="52"/>
+      <c r="B17" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D17" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40" t="s">
+      <c r="E17" s="38"/>
+      <c r="F17" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="46"/>
-      <c r="B18" s="33" t="s">
+      <c r="A18" s="53"/>
+      <c r="B18" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40" t="s">
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="H18" s="40"/>
+      <c r="H18" s="38"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D19" s="45" t="s">
+      <c r="D19" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40" t="s">
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2836,7 +2811,7 @@
       <c r="F1" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="32" t="s">
         <v>192</v>
       </c>
       <c r="H1" s="30" t="s">
@@ -2859,218 +2834,218 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="D2" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="E2" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="F2" s="40" t="s">
+      <c r="C2" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E2" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="F2" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="J2" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="K2" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L2" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M2" s="41">
+      <c r="J2" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="K2" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L2" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M2" s="39">
         <v>0.15</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="D3" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="F3" s="40" t="s">
+      <c r="C3" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="J3" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="K3" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="L3" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M3" s="41">
+      <c r="J3" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="K3" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="L3" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M3" s="39">
         <v>0.1</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="E4" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="40" t="s">
+      <c r="C4" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="J4" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="K4" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L4" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="M4" s="41">
+      <c r="J4" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L4" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="M4" s="39">
         <v>0.2</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="F5" s="40" t="s">
+      <c r="C5" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="F5" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="J5" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="K5" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="L5" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="M5" s="41">
+      <c r="J5" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="L5" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="M5" s="39">
         <v>0.3</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="F6" s="40" t="s">
+      <c r="C6" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="J6" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="K6" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L6" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M6" s="41">
+      <c r="J6" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="K6" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L6" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M6" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="49"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="43"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="49"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="43"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="49"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="43"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
@@ -3078,13 +3053,13 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="32" t="s">
         <v>153</v>
       </c>
       <c r="D12" s="30" t="s">
@@ -3105,7 +3080,7 @@
       <c r="I12" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="J12" s="38" t="s">
+      <c r="J12" s="36" t="s">
         <v>271</v>
       </c>
       <c r="K12" s="30" t="s">
@@ -3125,8 +3100,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="51"/>
-      <c r="B13" s="33" t="s">
+      <c r="A13" s="54"/>
+      <c r="B13" s="31" t="s">
         <v>259</v>
       </c>
       <c r="D13" s="30" t="s">
@@ -3147,25 +3122,25 @@
       <c r="I13" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="K13" s="40" t="s">
+      <c r="K13" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="L13" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M13" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="N13" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="O13" s="41">
+      <c r="L13" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M13" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="N13" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="O13" s="39">
         <v>0.3</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="51"/>
-      <c r="B14" s="33" t="s">
+      <c r="A14" s="54"/>
+      <c r="B14" s="31" t="s">
         <v>260</v>
       </c>
       <c r="D14" s="30" t="s">
@@ -3186,27 +3161,27 @@
       <c r="I14" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="K14" s="40" t="s">
+      <c r="K14" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="L14" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N14" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="O14" s="41">
+      <c r="L14" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M14" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="N14" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="O14" s="39">
         <v>0.2</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="31" t="s">
         <v>261</v>
       </c>
       <c r="D15" s="30" t="s">
@@ -3227,25 +3202,25 @@
       <c r="I15" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="K15" s="40" t="s">
+      <c r="K15" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="L15" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="M15" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N15" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="O15" s="41">
+      <c r="L15" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="M15" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="N15" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="O15" s="39">
         <v>0.15</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
-      <c r="B16" s="33" t="s">
+      <c r="A16" s="52"/>
+      <c r="B16" s="31" t="s">
         <v>262</v>
       </c>
       <c r="D16" s="30" t="s">
@@ -3258,25 +3233,25 @@
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
       <c r="I16" s="31"/>
-      <c r="K16" s="40" t="s">
+      <c r="K16" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="L16" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M16" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="N16" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="O16" s="41">
+      <c r="L16" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M16" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="N16" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="O16" s="39">
         <v>0.1</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="44"/>
-      <c r="B17" s="33" t="s">
+      <c r="A17" s="52"/>
+      <c r="B17" s="31" t="s">
         <v>263</v>
       </c>
       <c r="D17" s="30" t="s">
@@ -3289,25 +3264,25 @@
       <c r="G17" s="31"/>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
-      <c r="K17" s="40" t="s">
+      <c r="K17" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="L17" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M17" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N17" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="O17" s="41">
+      <c r="L17" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M17" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="N17" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="O17" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="44"/>
-      <c r="B18" s="33" t="s">
+      <c r="A18" s="52"/>
+      <c r="B18" s="31" t="s">
         <v>264</v>
       </c>
       <c r="D18" s="30" t="s">
@@ -3322,8 +3297,8 @@
       <c r="I18" s="31"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="46"/>
-      <c r="B19" s="52" t="s">
+      <c r="A19" s="53"/>
+      <c r="B19" s="45" t="s">
         <v>265</v>
       </c>
       <c r="D19" s="30" t="s">
@@ -3377,22 +3352,22 @@
       <c r="A1" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="40" t="s">
         <v>272</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="40" t="s">
         <v>273</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="40" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="47" t="s">
         <v>286</v>
       </c>
       <c r="H1" s="30" t="s">
@@ -3415,196 +3390,196 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="38" t="s">
         <v>275</v>
       </c>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40" t="s">
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="J2" s="40">
+      <c r="J2" s="38">
         <v>500</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40" t="s">
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="38" t="s">
         <v>276</v>
       </c>
-      <c r="D3" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40" t="s">
+      <c r="D3" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="J3" s="40">
+      <c r="J3" s="38">
         <v>200</v>
       </c>
-      <c r="K3" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40" t="s">
+      <c r="K3" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="38" t="s">
         <v>276</v>
       </c>
-      <c r="D4" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="E4" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="F4" s="40" t="s">
+      <c r="D4" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="38" t="s">
         <v>278</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="J4" s="40">
+      <c r="J4" s="38">
         <v>200</v>
       </c>
-      <c r="K4" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="L4" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M4" s="40" t="s">
+      <c r="K4" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="L4" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M4" s="38" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="38" t="s">
         <v>276</v>
       </c>
-      <c r="D5" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="F5" s="40" t="s">
+      <c r="D5" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="F5" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="38">
         <v>200</v>
       </c>
-      <c r="K5" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="L5" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="M5" s="40" t="s">
+      <c r="K5" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="L5" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="M5" s="38" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="F6" s="40" t="s">
+      <c r="D6" s="38"/>
+      <c r="E6" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="J6" s="40">
+      <c r="J6" s="38">
         <v>50</v>
       </c>
-      <c r="K6" s="40" t="s">
+      <c r="K6" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="L6" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="M6" s="40" t="s">
+      <c r="L6" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="M6" s="38" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="F7" s="40" t="s">
+      <c r="D7" s="38"/>
+      <c r="E7" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" s="38" t="s">
         <v>278</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="H7" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="I7" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="J7" s="40">
+      <c r="J7" s="38">
         <v>50</v>
       </c>
-      <c r="K7" s="40" t="s">
+      <c r="K7" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="L7" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="M7" s="40" t="s">
+      <c r="L7" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="M7" s="38" t="s">
         <v>278</v>
       </c>
     </row>
@@ -3612,18 +3587,18 @@
       <c r="A8" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="48" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="55" t="s">
         <v>280</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="C9" s="53">
+      <c r="C9" s="46">
         <v>1</v>
       </c>
       <c r="E9" s="30" t="s">
@@ -3637,11 +3612,11 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="57"/>
-      <c r="B10" s="32" t="s">
+      <c r="A10" s="56"/>
+      <c r="B10" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="46">
         <v>1000</v>
       </c>
       <c r="E10" s="31" t="s">
@@ -3655,9 +3630,9 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="50"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
       <c r="E11" s="31" t="s">
         <v>200</v>
       </c>
@@ -3669,7 +3644,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="51" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="30" t="s">
@@ -3689,7 +3664,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="31" t="s">
         <v>283</v>
       </c>
@@ -3707,7 +3682,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="31" t="s">
         <v>284</v>
       </c>
@@ -3725,7 +3700,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="44"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="31" t="s">
         <v>11</v>
       </c>
@@ -3743,7 +3718,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="31" t="s">
         <v>12</v>
       </c>
@@ -3761,7 +3736,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="44"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="31" t="s">
         <v>285</v>
       </c>
@@ -3770,7 +3745,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="44"/>
+      <c r="A18" s="52"/>
       <c r="B18" s="31" t="s">
         <v>15</v>
       </c>
@@ -3779,7 +3754,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="46"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="31" t="s">
         <v>14</v>
       </c>
@@ -3791,13 +3766,13 @@
       <c r="A21" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="45" t="s">
         <v>293</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D21" s="35" t="s">
         <v>153</v>
       </c>
       <c r="E21" s="30" t="s">
@@ -3818,7 +3793,7 @@
       <c r="J21" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="K21" s="39" t="s">
+      <c r="K21" s="37" t="s">
         <v>304</v>
       </c>
       <c r="L21" s="30" t="s">
@@ -3841,238 +3816,238 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="59"/>
-      <c r="C22" s="52" t="s">
+      <c r="B22" s="58"/>
+      <c r="C22" s="45" t="s">
         <v>294</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="F22" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="G22" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H22" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="I22" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="J22" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L22" s="40" t="s">
+      <c r="F22" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="H22" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I22" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="J22" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L22" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="M22" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="N22" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="40" t="s">
+      <c r="M22" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="N22" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B23" s="59"/>
-      <c r="C23" s="52" t="s">
+      <c r="B23" s="58"/>
+      <c r="C23" s="45" t="s">
         <v>295</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="F23" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G23" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H23" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="I23" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="J23" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L23" s="40" t="s">
+      <c r="F23" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H23" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="J23" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L23" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="M23" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N23" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="O23" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="40" t="s">
+      <c r="M23" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="N23" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="O23" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B24" s="60"/>
-      <c r="C24" s="52" t="s">
+      <c r="B24" s="59"/>
+      <c r="C24" s="45" t="s">
         <v>296</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="L24" s="40" t="s">
+      <c r="F24" s="38"/>
+      <c r="G24" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="L24" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="M24" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N24" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="O24" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="P24" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q24" s="40" t="s">
+      <c r="M24" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="N24" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="O24" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="P24" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q24" s="38" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="60" t="s">
         <v>171</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="45" t="s">
         <v>297</v>
       </c>
-      <c r="E25" s="40" t="s">
+      <c r="E25" s="38" t="s">
         <v>300</v>
       </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="I25" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="J25" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="L25" s="40" t="s">
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I25" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="J25" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="L25" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="M25" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N25" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="O25" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="P25" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q25" s="40" t="s">
+      <c r="M25" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="N25" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="O25" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="P25" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q25" s="38" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="62"/>
-      <c r="C26" s="52" t="s">
+      <c r="B26" s="61"/>
+      <c r="C26" s="45" t="s">
         <v>299</v>
       </c>
-      <c r="E26" s="45" t="s">
+      <c r="E26" s="40" t="s">
         <v>301</v>
       </c>
-      <c r="F26" s="40" t="s">
+      <c r="F26" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40" t="s">
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="J26" s="40"/>
-      <c r="L26" s="40" t="s">
+      <c r="J26" s="38"/>
+      <c r="L26" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="M26" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N26" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="O26" s="40"/>
-      <c r="P26" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q26" s="40" t="s">
+      <c r="M26" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="N26" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q26" s="38" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="63"/>
-      <c r="C27" s="52" t="s">
+      <c r="B27" s="62"/>
+      <c r="C27" s="45" t="s">
         <v>298</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="40" t="s">
         <v>302</v>
       </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40" t="s">
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40" t="s">
+      <c r="I27" s="38"/>
+      <c r="J27" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="L27" s="40" t="s">
+      <c r="L27" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="M27" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N27" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="O27" s="40"/>
-      <c r="P27" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q27" s="40" t="s">
+      <c r="M27" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="N27" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="O27" s="38"/>
+      <c r="P27" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q27" s="38" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="E28" s="45" t="s">
+      <c r="E28" s="40" t="s">
         <v>303</v>
       </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40" t="s">
+      <c r="F28" s="38"/>
+      <c r="G28" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4117,7 +4092,7 @@
       <c r="E1" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="47" t="s">
         <v>286</v>
       </c>
       <c r="G1" s="30" t="s">
@@ -4137,118 +4112,118 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="38" t="s">
         <v>307</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="38" t="s">
         <v>308</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="38" t="s">
         <v>309</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="38" t="s">
         <v>307</v>
       </c>
-      <c r="J2" s="40">
+      <c r="J2" s="38">
         <v>30</v>
       </c>
-      <c r="K2" s="40">
+      <c r="K2" s="38">
         <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="38" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="38" t="s">
         <v>312</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="38" t="s">
         <v>310</v>
       </c>
-      <c r="J3" s="40">
+      <c r="J3" s="38">
         <v>20</v>
       </c>
-      <c r="K3" s="40">
+      <c r="K3" s="38">
         <v>3000</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="38" t="s">
         <v>310</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="38" t="s">
         <v>313</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="38" t="s">
         <v>314</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="38" t="s">
         <v>310</v>
       </c>
-      <c r="J4" s="40">
+      <c r="J4" s="38">
         <v>40</v>
       </c>
-      <c r="K4" s="40">
+      <c r="K4" s="38">
         <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="38" t="s">
         <v>315</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="38" t="s">
         <v>316</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="38" t="s">
         <v>307</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="38">
         <v>70</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="38">
         <v>1500</v>
       </c>
     </row>
@@ -4258,27 +4233,27 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="55" t="s">
         <v>280</v>
       </c>
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57"/>
-      <c r="B9" s="64" t="s">
+      <c r="A9" s="56"/>
+      <c r="B9" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="33">
         <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="55" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="30" t="s">
@@ -4287,7 +4262,7 @@
       <c r="C11" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="56" t="s">
+      <c r="E11" s="55" t="s">
         <v>221</v>
       </c>
       <c r="F11" s="30" t="s">
@@ -4304,14 +4279,14 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="65"/>
-      <c r="B12" s="40" t="s">
+      <c r="A12" s="63"/>
+      <c r="B12" s="38" t="s">
         <v>284</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="38">
         <v>0</v>
       </c>
-      <c r="E12" s="65"/>
+      <c r="E12" s="63"/>
       <c r="F12" s="31" t="s">
         <v>199</v>
       </c>
@@ -4326,14 +4301,14 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="65"/>
-      <c r="B13" s="40" t="s">
+      <c r="A13" s="63"/>
+      <c r="B13" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="38">
         <v>1</v>
       </c>
-      <c r="E13" s="65"/>
+      <c r="E13" s="63"/>
       <c r="F13" s="31" t="s">
         <v>200</v>
       </c>
@@ -4348,14 +4323,14 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="65"/>
-      <c r="B14" s="40" t="s">
+      <c r="A14" s="63"/>
+      <c r="B14" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="38">
         <v>24</v>
       </c>
-      <c r="E14" s="65"/>
+      <c r="E14" s="63"/>
       <c r="F14" s="31" t="s">
         <v>201</v>
       </c>
@@ -4370,14 +4345,14 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="65"/>
-      <c r="B15" s="40" t="s">
+      <c r="A15" s="63"/>
+      <c r="B15" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="38">
         <v>25</v>
       </c>
-      <c r="E15" s="65"/>
+      <c r="E15" s="63"/>
       <c r="F15" s="31" t="s">
         <v>202</v>
       </c>
@@ -4392,14 +4367,14 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="65"/>
-      <c r="B16" s="40" t="s">
+      <c r="A16" s="63"/>
+      <c r="B16" s="38" t="s">
         <v>323</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="38">
         <v>64</v>
       </c>
-      <c r="E16" s="65"/>
+      <c r="E16" s="63"/>
       <c r="F16" s="31" t="s">
         <v>203</v>
       </c>
@@ -4414,14 +4389,14 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="65"/>
-      <c r="B17" s="40" t="s">
+      <c r="A17" s="63"/>
+      <c r="B17" s="38" t="s">
         <v>324</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="38">
         <v>65</v>
       </c>
-      <c r="E17" s="65"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="31" t="s">
         <v>204</v>
       </c>
@@ -4436,14 +4411,14 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="57"/>
-      <c r="B18" s="40" t="s">
+      <c r="A18" s="56"/>
+      <c r="B18" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="38">
         <v>100</v>
       </c>
-      <c r="E18" s="65"/>
+      <c r="E18" s="63"/>
       <c r="F18" s="31" t="s">
         <v>236</v>
       </c>
@@ -4458,7 +4433,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E19" s="65"/>
+      <c r="E19" s="63"/>
       <c r="F19" s="31" t="s">
         <v>237</v>
       </c>
@@ -4473,7 +4448,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E20" s="57"/>
+      <c r="E20" s="56"/>
       <c r="F20" s="31" t="s">
         <v>327</v>
       </c>
@@ -4491,13 +4466,13 @@
       <c r="A22" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="B22" s="56" t="s">
+      <c r="B22" s="55" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="46" t="s">
         <v>328</v>
       </c>
-      <c r="D22" s="66" t="s">
+      <c r="D22" s="49" t="s">
         <v>153</v>
       </c>
       <c r="E22" s="30" t="s">
@@ -4517,147 +4492,147 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="65"/>
-      <c r="C23" s="53" t="s">
+      <c r="B23" s="63"/>
+      <c r="C23" s="46" t="s">
         <v>329</v>
       </c>
-      <c r="E23" s="45" t="s">
+      <c r="E23" s="40" t="s">
         <v>336</v>
       </c>
-      <c r="F23" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="G23" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H23" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="I23" s="40"/>
+      <c r="F23" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H23" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="65"/>
-      <c r="C24" s="53" t="s">
+      <c r="B24" s="63"/>
+      <c r="C24" s="46" t="s">
         <v>330</v>
       </c>
-      <c r="E24" s="45" t="s">
+      <c r="E24" s="40" t="s">
         <v>337</v>
       </c>
-      <c r="F24" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="G24" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" s="40" t="s">
+      <c r="F24" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="38" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="57"/>
-      <c r="C25" s="52" t="s">
+      <c r="B25" s="56"/>
+      <c r="C25" s="45" t="s">
         <v>331</v>
       </c>
-      <c r="E25" s="45" t="s">
+      <c r="E25" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G25" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H25" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="I25" s="40" t="s">
+      <c r="F25" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G25" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H25" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I25" s="38" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="53" t="s">
+      <c r="C26" s="46" t="s">
         <v>332</v>
       </c>
-      <c r="E26" s="45" t="s">
+      <c r="E26" s="40" t="s">
         <v>339</v>
       </c>
-      <c r="F26" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G26" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H26" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="I26" s="40" t="s">
+      <c r="F26" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G26" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="H26" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I26" s="38" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="65"/>
-      <c r="C27" s="53" t="s">
+      <c r="B27" s="63"/>
+      <c r="C27" s="46" t="s">
         <v>333</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="F27" s="40" t="s">
+      <c r="F27" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="65"/>
-      <c r="C28" s="53" t="s">
+      <c r="B28" s="63"/>
+      <c r="C28" s="46" t="s">
         <v>334</v>
       </c>
-      <c r="E28" s="45" t="s">
+      <c r="E28" s="40" t="s">
         <v>341</v>
       </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40" t="s">
+      <c r="F28" s="38"/>
+      <c r="G28" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="57"/>
-      <c r="C29" s="52" t="s">
+      <c r="B29" s="56"/>
+      <c r="C29" s="45" t="s">
         <v>335</v>
       </c>
-      <c r="E29" s="45" t="s">
+      <c r="E29" s="40" t="s">
         <v>342</v>
       </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40" t="s">
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="I29" s="40"/>
+      <c r="I29" s="38"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E30" s="45" t="s">
+      <c r="E30" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40" t="s">
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="55" t="s">
         <v>250</v>
       </c>
       <c r="B32" s="30" t="s">
@@ -4678,102 +4653,97 @@
       <c r="G32" s="30" t="s">
         <v>318</v>
       </c>
-      <c r="H32" s="67"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="65"/>
-      <c r="B33" s="40" t="s">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="63"/>
+      <c r="B33" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="C33" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="D33" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="E33" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="F33" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G33" s="40">
+      <c r="C33" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="D33" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="E33" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G33" s="38">
         <v>3000</v>
       </c>
-      <c r="H33" s="67"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="65"/>
-      <c r="B34" s="40" t="s">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="63"/>
+      <c r="B34" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="C34" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="E34" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="F34" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G34" s="40">
+      <c r="C34" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E34" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G34" s="38">
         <v>1000</v>
       </c>
-      <c r="H34" s="67"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="65"/>
-      <c r="B35" s="40" t="s">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="63"/>
+      <c r="B35" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="C35" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="D35" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="E35" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="F35" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G35" s="40">
+      <c r="C35" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E35" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G35" s="38">
         <v>500</v>
       </c>
-      <c r="H35" s="67"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="57"/>
-      <c r="B36" s="40" t="s">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="56"/>
+      <c r="B36" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="E36" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="F36" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="G36" s="40">
+      <c r="C36" s="38"/>
+      <c r="D36" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="G36" s="38">
         <v>1500</v>
       </c>
-      <c r="H36" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A32:A36"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A11:A18"/>
     <mergeCell ref="E11:E20"/>
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A32:A36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4811,7 +4781,7 @@
       <c r="E1" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="47" t="s">
         <v>286</v>
       </c>
       <c r="G1" s="30" t="s">
@@ -4831,118 +4801,118 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="38" t="s">
         <v>349</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="38" t="s">
         <v>350</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="38" t="s">
         <v>351</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="I2" s="40">
+      <c r="I2" s="38">
         <v>25</v>
       </c>
-      <c r="J2" s="40">
+      <c r="J2" s="38">
         <v>200</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="38" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="38" t="s">
         <v>350</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="38" t="s">
         <v>353</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="I3" s="40">
+      <c r="I3" s="38">
         <v>18</v>
       </c>
-      <c r="J3" s="40">
+      <c r="J3" s="38">
         <v>200</v>
       </c>
-      <c r="K3" s="40" t="s">
+      <c r="K3" s="38" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="38" t="s">
         <v>349</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="38" t="s">
         <v>354</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="38" t="s">
         <v>355</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="I4" s="40">
+      <c r="I4" s="38">
         <v>30</v>
       </c>
-      <c r="J4" s="40">
+      <c r="J4" s="38">
         <v>50</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="K4" s="38" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="38" t="s">
         <v>354</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="38" t="s">
         <v>356</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="38">
         <v>18</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="38">
         <v>50</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" s="38" t="s">
         <v>356</v>
       </c>
     </row>
@@ -4952,48 +4922,48 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="55" t="s">
         <v>280</v>
       </c>
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="C8" s="64">
+      <c r="C8" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="65"/>
-      <c r="B9" s="64" t="s">
+      <c r="A9" s="63"/>
+      <c r="B9" s="38" t="s">
         <v>359</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="33">
         <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="65"/>
-      <c r="B10" s="64" t="s">
+      <c r="A10" s="63"/>
+      <c r="B10" s="38" t="s">
         <v>360</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A11" s="57"/>
-      <c r="B11" s="64" t="s">
+      <c r="A11" s="56"/>
+      <c r="B11" s="38" t="s">
         <v>361</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="33">
         <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="64" t="s">
         <v>100</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -5022,11 +4992,11 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B14" s="69"/>
-      <c r="C14" s="40" t="s">
+      <c r="B14" s="65"/>
+      <c r="C14" s="38" t="s">
         <v>284</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="38">
         <v>0</v>
       </c>
       <c r="F14" s="31" t="s">
@@ -5046,11 +5016,11 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B15" s="69"/>
-      <c r="C15" s="40" t="s">
+      <c r="B15" s="65"/>
+      <c r="C15" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="38">
         <v>1</v>
       </c>
       <c r="F15" s="31" t="s">
@@ -5070,11 +5040,11 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B16" s="69"/>
-      <c r="C16" s="40" t="s">
+      <c r="B16" s="65"/>
+      <c r="C16" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="38">
         <v>20</v>
       </c>
       <c r="F16" s="31" t="s">
@@ -5094,11 +5064,11 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B17" s="69"/>
-      <c r="C17" s="40" t="s">
+      <c r="B17" s="65"/>
+      <c r="C17" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="38">
         <v>21</v>
       </c>
       <c r="F17" s="31" t="s">
@@ -5118,11 +5088,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B18" s="70"/>
-      <c r="C18" s="40" t="s">
+      <c r="B18" s="66"/>
+      <c r="C18" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="38">
         <v>100</v>
       </c>
       <c r="F18" s="31" t="s">
@@ -5142,13 +5112,13 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B19" s="71" t="s">
+      <c r="B19" s="67" t="s">
         <v>348</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="38" t="s">
         <v>284</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="38">
         <v>0</v>
       </c>
       <c r="F19" s="31" t="s">
@@ -5168,11 +5138,11 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B20" s="72"/>
-      <c r="C20" s="40" t="s">
+      <c r="B20" s="68"/>
+      <c r="C20" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="38">
         <v>1</v>
       </c>
       <c r="F20" s="31" t="s">
@@ -5192,47 +5162,47 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="72"/>
-      <c r="C21" s="40" t="s">
+      <c r="B21" s="68"/>
+      <c r="C21" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="38">
         <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="72"/>
-      <c r="C22" s="40" t="s">
+      <c r="B22" s="68"/>
+      <c r="C22" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="38">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="73"/>
-      <c r="C23" s="40" t="s">
+      <c r="B23" s="69"/>
+      <c r="C23" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="40">
+      <c r="D23" s="38">
         <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="55" t="s">
         <v>173</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="31" t="s">
         <v>370</v>
       </c>
-      <c r="E25" s="37" t="s">
+      <c r="E25" s="35" t="s">
         <v>153</v>
       </c>
       <c r="F25" s="30" t="s">
@@ -5252,102 +5222,102 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B26" s="57"/>
-      <c r="C26" s="33" t="s">
+      <c r="B26" s="56"/>
+      <c r="C26" s="31" t="s">
         <v>371</v>
       </c>
-      <c r="F26" s="45" t="s">
+      <c r="F26" s="40" t="s">
         <v>372</v>
       </c>
-      <c r="G26" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H26" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="I26" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="J26" s="40" t="s">
+      <c r="G26" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I26" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="J26" s="38" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="31" t="s">
         <v>351</v>
       </c>
-      <c r="F27" s="45" t="s">
+      <c r="F27" s="40" t="s">
         <v>373</v>
       </c>
-      <c r="G27" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H27" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="I27" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="J27" s="40" t="s">
+      <c r="G27" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H27" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I27" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="J27" s="38" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="65"/>
-      <c r="C28" s="33" t="s">
+      <c r="B28" s="63"/>
+      <c r="C28" s="31" t="s">
         <v>353</v>
       </c>
-      <c r="F28" s="45" t="s">
+      <c r="F28" s="40" t="s">
         <v>374</v>
       </c>
-      <c r="G28" s="40" t="s">
+      <c r="G28" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="65"/>
-      <c r="C29" s="33" t="s">
+      <c r="B29" s="63"/>
+      <c r="C29" s="31" t="s">
         <v>355</v>
       </c>
-      <c r="F29" s="45" t="s">
+      <c r="F29" s="40" t="s">
         <v>375</v>
       </c>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40" t="s">
+      <c r="G29" s="38"/>
+      <c r="H29" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="38"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="57"/>
-      <c r="C30" s="33" t="s">
+      <c r="B30" s="56"/>
+      <c r="C30" s="31" t="s">
         <v>356</v>
       </c>
-      <c r="F30" s="45" t="s">
+      <c r="F30" s="40" t="s">
         <v>376</v>
       </c>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40" t="s">
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="J30" s="40"/>
+      <c r="J30" s="38"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F31" s="45" t="s">
+      <c r="F31" s="40" t="s">
         <v>377</v>
       </c>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40" t="s">
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38" t="s">
         <v>172</v>
       </c>
     </row>
@@ -5369,58 +5339,58 @@
       </c>
     </row>
     <row r="34" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="F34" s="40" t="s">
+      <c r="F34" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="G34" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H34" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="I34" s="40" t="s">
+      <c r="G34" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H34" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I34" s="38" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="35" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="F35" s="40" t="s">
+      <c r="F35" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="G35" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H35" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="I35" s="40" t="s">
+      <c r="G35" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I35" s="38" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="36" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="F36" s="40" t="s">
+      <c r="F36" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="G36" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H36" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="I36" s="40" t="s">
+      <c r="G36" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H36" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I36" s="38" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="37" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="F37" s="40" t="s">
+      <c r="F37" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="G37" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H37" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="I37" s="40" t="s">
+      <c r="G37" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="H37" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I37" s="38" t="s">
         <v>356</v>
       </c>
     </row>
@@ -5457,7 +5427,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>132</v>
       </c>
       <c r="B1" s="30" t="s">
@@ -5481,7 +5451,7 @@
       <c r="H1" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="37" t="s">
         <v>192</v>
       </c>
       <c r="J1" s="30" t="s">
@@ -5517,16 +5487,16 @@
       <c r="H2" s="31" t="s">
         <v>384</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="38" t="s">
         <v>388</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="38" t="s">
         <v>384</v>
       </c>
     </row>
@@ -5552,16 +5522,16 @@
       <c r="H3" s="31" t="s">
         <v>384</v>
       </c>
-      <c r="J3" s="40" t="s">
+      <c r="J3" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="K3" s="40" t="s">
+      <c r="K3" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="38" t="s">
         <v>389</v>
       </c>
-      <c r="M3" s="40" t="s">
+      <c r="M3" s="38" t="s">
         <v>384</v>
       </c>
     </row>
@@ -5587,16 +5557,16 @@
       <c r="H4" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="40" t="s">
+      <c r="J4" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="K4" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="L4" s="40" t="s">
+      <c r="L4" s="38" t="s">
         <v>390</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="M4" s="38" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5616,16 +5586,16 @@
       <c r="H5" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="J5" s="40" t="s">
+      <c r="J5" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="L5" s="40" t="s">
+      <c r="L5" s="38" t="s">
         <v>385</v>
       </c>
-      <c r="M5" s="40" t="s">
+      <c r="M5" s="38" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5645,16 +5615,16 @@
       <c r="H6" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="J6" s="40" t="s">
+      <c r="J6" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="K6" s="40" t="s">
+      <c r="K6" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="L6" s="40" t="s">
+      <c r="L6" s="38" t="s">
         <v>386</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="38" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5672,16 +5642,16 @@
       <c r="H7" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="J7" s="40" t="s">
+      <c r="J7" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="K7" s="40" t="s">
+      <c r="K7" s="38" t="s">
         <v>151</v>
       </c>
-      <c r="L7" s="40" t="s">
+      <c r="L7" s="38" t="s">
         <v>391</v>
       </c>
-      <c r="M7" s="40" t="s">
+      <c r="M7" s="38" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5703,16 +5673,16 @@
       <c r="H8" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="J8" s="40" t="s">
+      <c r="J8" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="K8" s="40" t="s">
+      <c r="K8" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="L8" s="40" t="s">
+      <c r="L8" s="38" t="s">
         <v>392</v>
       </c>
-      <c r="M8" s="40" t="s">
+      <c r="M8" s="38" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5722,22 +5692,22 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="55" t="s">
         <v>280</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="31" t="s">
         <v>396</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="31" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A12" s="57"/>
-      <c r="B12" s="33" t="s">
+      <c r="A12" s="56"/>
+      <c r="B12" s="31" t="s">
         <v>394</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="31" t="s">
         <v>395</v>
       </c>
     </row>
@@ -5768,10 +5738,10 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="38" t="s">
         <v>398</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="38">
         <v>99</v>
       </c>
       <c r="E15" s="31" t="s">
@@ -5788,10 +5758,10 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="38" t="s">
         <v>399</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="38">
         <v>100</v>
       </c>
       <c r="E16" s="31" t="s">
@@ -5808,10 +5778,10 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="38" t="s">
         <v>400</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="38">
         <v>101</v>
       </c>
       <c r="E17" s="31" t="s">
@@ -5828,10 +5798,10 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="38" t="s">
         <v>401</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="38">
         <v>110</v>
       </c>
       <c r="E18" s="31" t="s">
@@ -5848,10 +5818,10 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="38" t="s">
         <v>402</v>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="38">
         <v>111</v>
       </c>
       <c r="E19" s="31" t="s">
@@ -5871,14 +5841,14 @@
       <c r="A21" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="33" t="s">
         <v>405</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="42" t="s">
+      <c r="D21" s="33"/>
+      <c r="E21" s="32" t="s">
         <v>153</v>
       </c>
       <c r="F21" s="30" t="s">
@@ -5901,148 +5871,148 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="76"/>
-      <c r="C22" s="35" t="s">
+      <c r="B22" s="52"/>
+      <c r="C22" s="33" t="s">
         <v>406</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="F22" s="45" t="s">
+      <c r="D22" s="33"/>
+      <c r="F22" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="G22" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H22" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="I22" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="J22" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="K22" s="40" t="s">
+      <c r="G22" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H22" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I22" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="J22" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="K22" s="38" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="76"/>
-      <c r="C23" s="35" t="s">
+      <c r="B23" s="52"/>
+      <c r="C23" s="33" t="s">
         <v>407</v>
       </c>
-      <c r="D23" s="35"/>
-      <c r="F23" s="45" t="s">
+      <c r="D23" s="33"/>
+      <c r="F23" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="G23" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H23" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="I23" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="J23" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="K23" s="40"/>
+      <c r="G23" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H23" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="J23" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="K23" s="38"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="76"/>
-      <c r="C24" s="35" t="s">
+      <c r="B24" s="52"/>
+      <c r="C24" s="33" t="s">
         <v>408</v>
       </c>
-      <c r="D24" s="35"/>
-      <c r="F24" s="45" t="s">
+      <c r="D24" s="33"/>
+      <c r="F24" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="G24" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H24" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
+      <c r="G24" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="H24" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="77"/>
-      <c r="C25" s="78" t="s">
+      <c r="B25" s="53"/>
+      <c r="C25" s="50" t="s">
         <v>409</v>
       </c>
-      <c r="D25" s="35"/>
-      <c r="F25" s="45" t="s">
+      <c r="D25" s="33"/>
+      <c r="F25" s="40" t="s">
         <v>300</v>
       </c>
-      <c r="G25" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="I25" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
+      <c r="G25" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I25" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="35" t="s">
+      <c r="C26" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="D26" s="35"/>
-      <c r="F26" s="45" t="s">
+      <c r="D26" s="33"/>
+      <c r="F26" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="I26" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I26" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="57"/>
-      <c r="C27" s="35" t="s">
+      <c r="B27" s="56"/>
+      <c r="C27" s="33" t="s">
         <v>411</v>
       </c>
-      <c r="D27" s="35"/>
-      <c r="F27" s="45" t="s">
+      <c r="D27" s="33"/>
+      <c r="F27" s="40" t="s">
         <v>413</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="H27" s="40" t="s">
+      <c r="H27" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
     </row>
     <row r="28" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="F28" s="45" t="s">
+      <c r="F28" s="40" t="s">
         <v>414</v>
       </c>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40" t="s">
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="J28" s="40" t="s">
+      <c r="J28" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="K28" s="40" t="s">
+      <c r="K28" s="38" t="s">
         <v>172</v>
       </c>
     </row>
@@ -6061,57 +6031,57 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="40" t="s">
+      <c r="B30" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="D30" s="40" t="s">
+      <c r="D30" s="38" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="40" t="s">
+      <c r="B31" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="D31" s="40" t="s">
+      <c r="D31" s="38" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="40" t="s">
+      <c r="B32" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="D32" s="40" t="s">
+      <c r="D32" s="38" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D33" s="40" t="s">
+      <c r="D33" s="38" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="C34" s="40" t="s">
+      <c r="C34" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="D34" s="40" t="s">
+      <c r="D34" s="38" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7848,10 +7818,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="32" t="s">
         <v>192</v>
       </c>
     </row>
@@ -8210,10 +8180,10 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="32" t="s">
         <v>153</v>
       </c>
       <c r="D16" s="30" t="s">
@@ -8234,7 +8204,7 @@
       <c r="I16" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="K16" s="38" t="s">
+      <c r="K16" s="36" t="s">
         <v>16</v>
       </c>
       <c r="L16" s="30" t="s">
@@ -8254,10 +8224,10 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="31" t="s">
         <v>176</v>
       </c>
       <c r="D17" s="31" t="s">
@@ -8293,8 +8263,8 @@
       </c>
     </row>
     <row r="18" spans="1:16" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
-      <c r="B18" s="33" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="31" t="s">
         <v>174</v>
       </c>
       <c r="D18" s="31" t="s">
@@ -8326,8 +8296,8 @@
       </c>
     </row>
     <row r="19" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
-      <c r="B19" s="33" t="s">
+      <c r="A19" s="33"/>
+      <c r="B19" s="31" t="s">
         <v>175</v>
       </c>
       <c r="D19" s="31" t="s">
@@ -8359,10 +8329,10 @@
       </c>
     </row>
     <row r="20" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="31" t="s">
         <v>177</v>
       </c>
       <c r="D20" s="30" t="s">
@@ -8390,8 +8360,8 @@
       </c>
     </row>
     <row r="21" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A21" s="35"/>
-      <c r="B21" s="33" t="s">
+      <c r="A21" s="33"/>
+      <c r="B21" s="31" t="s">
         <v>178</v>
       </c>
       <c r="D21" s="30" t="s">
@@ -8406,8 +8376,8 @@
       <c r="I21" s="31"/>
     </row>
     <row r="22" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
-      <c r="B22" s="33" t="s">
+      <c r="A22" s="33"/>
+      <c r="B22" s="31" t="s">
         <v>179</v>
       </c>
       <c r="D22" s="30" t="s">
@@ -8422,8 +8392,8 @@
       <c r="I22" s="31"/>
     </row>
     <row r="23" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A23" s="35"/>
-      <c r="B23" s="33" t="s">
+      <c r="A23" s="33"/>
+      <c r="B23" s="31" t="s">
         <v>180</v>
       </c>
       <c r="D23" s="30" t="s">
